--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -11138,16 +11138,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>SAVERIO WG BIANCO</t>
-        </is>
-      </c>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -11158,10 +11154,10 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4154</v>
+        <v>-256</v>
       </c>
       <c r="J195" t="n">
-        <v>1076</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -11173,7 +11169,7 @@
         <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>228.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -7430,19 +7430,15 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>SAVERIO WG BIANCO</t>
-        </is>
-      </c>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>7825</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -7450,10 +7446,10 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>20345</v>
+        <v>-1436</v>
       </c>
       <c r="J128" t="n">
-        <v>7237</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -7465,7 +7461,7 @@
         <v>0.2</v>
       </c>
       <c r="N128" t="n">
-        <v>1075.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -10918,30 +10918,26 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>SAVERIO WG BIANCO</t>
-        </is>
-      </c>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>3494</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>12212</v>
+        <v>-191</v>
       </c>
       <c r="J191" t="n">
-        <v>3413</v>
+        <v>0</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -10953,7 +10949,7 @@
         <v>0.8</v>
       </c>
       <c r="N191" t="n">
-        <v>172.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>1577.95</v>
+        <v>1216.29</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -6834,13 +6834,13 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>9892</v>
+        <v>-599</v>
       </c>
       <c r="J117" t="n">
-        <v>3553</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
         <v>50</v>
@@ -6849,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="N117" t="n">
-        <v>500.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6879,24 +6879,24 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>500</v>
+        <v>284.75</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3561</v>
+        <v>-125</v>
       </c>
       <c r="J118" t="n">
-        <v>1481</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
         <v>50</v>
@@ -6905,7 +6905,7 @@
         <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>281.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -11182,19 +11182,15 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>SIMONE WG CEREA</t>
-        </is>
-      </c>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>1117</v>
+        <v>1943</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -11202,10 +11198,10 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3142</v>
+        <v>-262</v>
       </c>
       <c r="J196" t="n">
-        <v>762</v>
+        <v>0</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -11217,7 +11213,7 @@
         <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>125.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -5176,7 +5176,7 @@
         <v>337</v>
       </c>
       <c r="K87" t="n">
-        <v>1147</v>
+        <v>2577</v>
       </c>
       <c r="L87" t="n">
         <v>60</v>

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -2464,7 +2464,7 @@
         <v>2737</v>
       </c>
       <c r="K37" t="n">
-        <v>1724</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>4.2</v>
@@ -10776,7 +10776,7 @@
         <v>5350</v>
       </c>
       <c r="K188" t="n">
-        <v>4076</v>
+        <v>0</v>
       </c>
       <c r="L188" t="n">
         <v>4.2</v>

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -2438,30 +2438,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>SIMONE WG CEREA</t>
-        </is>
-      </c>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>=</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7690</v>
+        <v>-501</v>
       </c>
       <c r="J37" t="n">
-        <v>2737</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2473,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>322.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -10746,16 +10746,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>SIMONE WG CEREA</t>
-        </is>
-      </c>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
         <v>1800</v>
@@ -10766,10 +10762,10 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>15156</v>
+        <v>-555</v>
       </c>
       <c r="J188" t="n">
-        <v>5350</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -10781,7 +10777,7 @@
         <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>636.5599999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -2848,7 +2848,7 @@
         <v>2108</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1282</v>
       </c>
       <c r="L44" t="n">
         <v>76</v>

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -772,7 +772,7 @@
         <v>1383</v>
       </c>
       <c r="K6" t="n">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="L6" t="n">
         <v>4.5</v>
@@ -805,7 +805,11 @@
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FAUSTO WG LAI</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
@@ -1532,7 +1536,7 @@
         <v>1340</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L20" t="n">
         <v>8.5</v>
@@ -1717,7 +1721,11 @@
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FAUSTO WG LAI</t>
+        </is>
+      </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
@@ -2292,7 +2300,7 @@
         <v>2317</v>
       </c>
       <c r="K34" t="n">
-        <v>630</v>
+        <v>2975</v>
       </c>
       <c r="L34" t="n">
         <v>70</v>
@@ -2602,16 +2610,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2622,10 +2630,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>26924</v>
+        <v>-3761</v>
       </c>
       <c r="J40" t="n">
-        <v>9005</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2637,7 +2645,7 @@
         <v>0.6</v>
       </c>
       <c r="N40" t="n">
-        <v>1299.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2658,7 +2666,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2667,7 +2675,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2678,10 +2686,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5726</v>
+        <v>-47</v>
       </c>
       <c r="J41" t="n">
-        <v>2117</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2693,7 +2701,7 @@
         <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>256.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3016,7 +3024,7 @@
         <v>274</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L47" t="n">
         <v>7.3</v>
@@ -3072,7 +3080,7 @@
         <v>976</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="L48" t="n">
         <v>7.3</v>
@@ -3206,7 +3214,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3215,7 +3223,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3226,10 +3234,10 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1712</v>
+        <v>-38</v>
       </c>
       <c r="J51" t="n">
-        <v>1269</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3241,7 +3249,7 @@
         <v>2.2</v>
       </c>
       <c r="N51" t="n">
-        <v>403.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4096,7 +4104,7 @@
         <v>3632</v>
       </c>
       <c r="K67" t="n">
-        <v>655</v>
+        <v>2670</v>
       </c>
       <c r="L67" t="n">
         <v>55</v>
@@ -4609,7 +4617,11 @@
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>FAUSTO WG LAI</t>
+        </is>
+      </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
@@ -6004,7 +6016,7 @@
         <v>694</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="L102" t="n">
         <v>50</v>
@@ -6310,16 +6322,16 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -6330,13 +6342,13 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>12767</v>
+        <v>-1084</v>
       </c>
       <c r="J108" t="n">
-        <v>4040</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>1245</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>60</v>
@@ -6345,7 +6357,7 @@
         <v>1.8</v>
       </c>
       <c r="N108" t="n">
-        <v>386.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -7090,7 +7102,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7099,7 +7111,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -7110,10 +7122,10 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>7157</v>
+        <v>-318</v>
       </c>
       <c r="J122" t="n">
-        <v>2939</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -7125,7 +7137,7 @@
         <v>3.2</v>
       </c>
       <c r="N122" t="n">
-        <v>467.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -8336,7 +8348,7 @@
         <v>6279</v>
       </c>
       <c r="K144" t="n">
-        <v>3805</v>
+        <v>4965</v>
       </c>
       <c r="L144" t="n">
         <v>75</v>
@@ -8612,7 +8624,7 @@
         <v>1220</v>
       </c>
       <c r="K149" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="L149" t="n">
         <v>55</v>
@@ -9921,7 +9933,11 @@
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>LUCA WG ARABENI</t>
+        </is>
+      </c>
       <c r="F173" t="n">
         <v>0</v>
       </c>
@@ -10328,7 +10344,7 @@
         <v>1677</v>
       </c>
       <c r="K180" t="n">
-        <v>675</v>
+        <v>1725</v>
       </c>
       <c r="L180" t="n">
         <v>4</v>
@@ -10962,7 +10978,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10971,7 +10987,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -10982,13 +10998,13 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>20131</v>
+        <v>-3127</v>
       </c>
       <c r="J192" t="n">
-        <v>6246</v>
+        <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>1810</v>
+        <v>0</v>
       </c>
       <c r="L192" t="n">
         <v>55</v>
@@ -10997,7 +11013,7 @@
         <v>1.4</v>
       </c>
       <c r="N192" t="n">
-        <v>534.4299999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -11044,7 +11060,7 @@
         <v>1260</v>
       </c>
       <c r="K193" t="n">
-        <v>0</v>
+        <v>1710</v>
       </c>
       <c r="L193" t="n">
         <v>70</v>
@@ -11133,7 +11149,11 @@
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>RICCARDO WG ROSSO</t>
+        </is>
+      </c>
       <c r="F195" t="n">
         <v>0</v>
       </c>
@@ -11577,7 +11597,11 @@
           <t>09/10/2026</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>FAUSTO WG LAI</t>
+        </is>
+      </c>
       <c r="F203" t="n">
         <v>0</v>
       </c>

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -1528,7 +1528,7 @@
         <v>7265</v>
       </c>
       <c r="K20" t="n">
-        <v>2000</v>
+        <v>7987</v>
       </c>
       <c r="L20" t="n">
         <v>8.5</v>
@@ -5392,7 +5392,7 @@
         <v>2178</v>
       </c>
       <c r="K91" t="n">
-        <v>1055</v>
+        <v>1960</v>
       </c>
       <c r="L91" t="n">
         <v>60</v>
@@ -9850,16 +9850,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>RICCARDO WG ROSSO</t>
-        </is>
-      </c>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -9870,10 +9866,10 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4856</v>
+        <v>-27</v>
       </c>
       <c r="J172" t="n">
-        <v>1717</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -9885,7 +9881,7 @@
         <v>1.3</v>
       </c>
       <c r="N172" t="n">
-        <v>224.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -2034,16 +2034,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>LUCA WG ARABENI</t>
-        </is>
-      </c>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2054,10 +2050,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2577</v>
+        <v>-685</v>
       </c>
       <c r="J30" t="n">
-        <v>859</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2069,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>110.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2080,7 +2076,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2248,7 +2244,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2640,7 +2636,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3300,7 +3296,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3668,7 +3664,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4388,7 +4384,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4852,7 +4848,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5244,7 +5240,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5804,7 +5800,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6016,7 +6012,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6292,7 +6288,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6348,7 +6344,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6732,7 +6728,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7460,7 +7456,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7572,7 +7568,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8172,7 +8168,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8238,16 +8234,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>LUCA WG ARABENI</t>
-        </is>
-      </c>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -8258,10 +8250,10 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>10039</v>
+        <v>-658</v>
       </c>
       <c r="J143" t="n">
-        <v>3425</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -8273,7 +8265,7 @@
         <v>3</v>
       </c>
       <c r="N143" t="n">
-        <v>380.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -8508,7 +8500,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8564,7 +8556,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8620,7 +8612,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8676,7 +8668,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9224,7 +9216,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9672,7 +9664,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10168,7 +10160,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10224,7 +10216,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10500,7 +10492,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10996,7 +10988,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11276,7 +11268,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SIMONE WG CEREA</t>
+          <t>DANIELE WG ACERBI</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11612,7 +11604,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>LUCA WG ARABENI</t>
+          <t>SAVERIO WG BIANCO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">

--- a/locali_non_incassati.xlsx
+++ b/locali_non_incassati.xlsx
@@ -7206,30 +7206,26 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>LUCA WG ARABENI</t>
-        </is>
-      </c>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>5122</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>+</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>11910</v>
+        <v>-1029</v>
       </c>
       <c r="J124" t="n">
-        <v>4444</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -7241,7 +7237,7 @@
         <v>2.6</v>
       </c>
       <c r="N124" t="n">
-        <v>590.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
